--- a/web/public/forms/orig/o-mijang-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-mijang-gyehoekseo.xlsx
@@ -886,7 +886,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="63" t="inlineStr">
@@ -3707,7 +3707,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="N1" s="63" t="inlineStr">
@@ -5129,7 +5129,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="63" t="inlineStr">
@@ -5916,7 +5916,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
@@ -12493,7 +12493,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -13281,7 +13281,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="63" t="inlineStr">
@@ -13378,7 +13378,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="63" t="inlineStr">
@@ -14711,7 +14711,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="63" t="inlineStr">

--- a/web/public/forms/orig/o-mijang-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-mijang-gyehoekseo.xlsx
@@ -855,7 +855,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
